--- a/Data/Numericals.xlsx
+++ b/Data/Numericals.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acldigital1-my.sharepoint.com/personal/sathishkumarr_acldigital1_onmicrosoft_com/Documents/Study/_NISM Certifications/_PGPFP/Course/Term 2/Research Analyst/Numericals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{85BC9775-B3CC-4C47-9973-3760C76C5C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5794E2E3-4C2E-4D28-8D36-2D734AB2469A}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{85BC9775-B3CC-4C47-9973-3760C76C5C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E685E9A-2920-4ED3-A7FF-55883D17C07D}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{B3B2EAEB-3D4F-44E9-A7BC-7C78BD8AFC15}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{B3B2EAEB-3D4F-44E9-A7BC-7C78BD8AFC15}"/>
   </bookViews>
   <sheets>
     <sheet name="Numericals 1" sheetId="1" r:id="rId1"/>
     <sheet name="Numericals 2" sheetId="2" r:id="rId2"/>
     <sheet name="Numericals 3" sheetId="3" r:id="rId3"/>
     <sheet name="Numericals 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Numericals 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Numericals 6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="300">
   <si>
     <t>Questiod_ID</t>
   </si>
@@ -944,6 +946,402 @@
   </si>
   <si>
     <t>Amaze Industries Ltd.'s PE ratio is 25x and PB ratio is negative</t>
+  </si>
+  <si>
+    <t>M/s. Microstrong has borrowed huge sums and has a debt of Rs. 500 crores. The interest payable on this is at 9% p.a. Calculate the Interest Coverage Ratio if the expected EBIT is Rs. 65 crores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Net Profit of a company was Rs 20 crores. The company's equity capital stood at Rs 3,44,81,540. The company has not issued any preference shares. The face value of its shares is Rs 10. Calculate the Earning Per Share (EPS) of the company. </t>
+  </si>
+  <si>
+    <t>Interest Coverage Ratio = EBIT / Interest Expense
+Intrerest expenses are 9% of 500 cr = 45 cr
+Interest Coverage Ratio = 65 cr / 45 cr = 1.44</t>
+  </si>
+  <si>
+    <t>EPS = Net Profit / No. of Shares
+First let's calculate the number of shares.
+Number of Shares = Equity Capital / Face Value
+= 3,44,81,540 / 10
+= 34,48,154
+EPS = Net Profit/ No. of Shares
+= 20,00,00,000 / 34,48,154
+= 58.00</t>
+  </si>
+  <si>
+    <t>The Return on Capital Employed (ROCE) of company M/s. Hightech Industries Ltd. is 8% and the cost of debt is 10%. What will be the most likely Return on Equity (ROE)?</t>
+  </si>
+  <si>
+    <t>ROCE is 8% but the cost of debt is 10%. Since the company earns less on its capital than it pays on borrowings, debt reduces overall returns. This drags down shareholder returns, so the ROE will end up below 8%.
+In other words:
+ROCE shows how efficiently the company earns on total capital, while cost of debt is what it pays on borrowings. Here, the company earns 8% but pays 10% on debt, so borrowing is costlier than returns. This creates negative leverage, which reduces returns for equity shareholders (ROE).
+Hence, the ROE will be lower than 8%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find out the Cost of Equity if the risk free rate is 7%, the market risk premium is 9% and the Beta is 0.60. </t>
+  </si>
+  <si>
+    <t>To find the Cost of Equity, we use the Capital Asset Pricing Model (CAPM) formula:
+Cost of Equity = Rf + ẞx (Rm-Rf)
+Where:
+• Rf = Risk-free rate = 7%
+• Rm - Rf = Market risk premium = 9% (Note: 'Rm - Rf' ie. the Market risk premium, is directly given as 9%) ẞ Beta = 0.60
+Substituting the value :
+Cost of Equity = 7% + (0.60 x 9%) = 7% + 5.4%
+= 12.4%</t>
+  </si>
+  <si>
+    <t>The Paid up capital of a company is Rs 5,00,000 with face value of Rs 10 per shares. The book value per share is Rs. 20 and the Dividend per share of the business is Rs 5. What is the Return on Capital Employed in the business?</t>
+  </si>
+  <si>
+    <t>Return on Capital Employed is similar to Return on Equity. Return on Equity = (Return Per Share / Book Value) x 100
+= 5/20 x 100 = 25%</t>
+  </si>
+  <si>
+    <t>The Price to earnings ratio of a company is 7. The EPS is Rs. 5 and the market capitalisation is Rs 7,00,000. The book value per share is Rs 24. What is the networth of the company?</t>
+  </si>
+  <si>
+    <t>Price to Earnings Ratio = Market Price of the share / EPS
+7 = Market Price of the share / 5
+Market Price of the share= 7 x 5 = Rs. 35
+Number of shares = Market Capitalisation / Market Price of share
+Number of shares = 700000 / 35 = 20,000
+Networth = Book Value x Number of shares
+= 24 x 20,000 Rs. 4,80,000</t>
+  </si>
+  <si>
+    <t>Calculate the SALES of a business if - EBITDA % of a business is 40%. Net profit is 20% of EBITDA. Dividend per share is Rs.2 and the dividend payout ratio is 40%. The number of outstanding shares are 10000.</t>
+  </si>
+  <si>
+    <t>Dividend paid per share is Rs. 2 and the number of outstanding shares are 10,000.
+So the total dividend paid is Rs. 2 X 10,000 = Rs.20,000
+The Dividend Payout ratio is 40%. This means Rs 20000 paid as divided is 40% of the Net Profit.
+So the Net Profit is Rs. 50000 (20000/40 x 100)
+The Net Profit is 20% of EBITDA.
+Rs 50000 is the Net Profit, So the EBITDA will be 50000/20 X 100 = 250000
+EBITDA is 40% of the business ie Sales.
+EBITDA is 250000. So Sales will be 250000 / 40 X 100 = 625000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XYZ Ltd. has Return on Capital Employed (ROCE) of 40% and Return on Equity (ROE) of 25%. The Net Profit is at Rs. 2,00,000 and the EBIT is at Rs. 4,00,000. Calculate the debt level in this business. </t>
+  </si>
+  <si>
+    <t>ROCE = EBIT / Capital Employed
+40% = 4,00,000/ Capital Employed
+Capital Employed = 400000/0.4 Rs. 10,00,000
+ROE = Net Profit/ Share Equity
+25% = 2,00,000/ Share Equity
+Share Equity = 200000 / 0.25 Rs. 8,00,000
+Debt = Total Capital Employed - Share Equity
+= 10,00,000 - 8,00,000
+= Rs. 2,00,000</t>
+  </si>
+  <si>
+    <t>The Market Capitalisation of a firm is Rs 1 lakh and it has a total debt of Rs 30,000. The cash in hand is Rs 5000. What is the Enterprise Value of the firm ?</t>
+  </si>
+  <si>
+    <t>Enterprise value (EV) = Market value of equity (Market capitalization) + Market value of debt - cash and cash equivalents
+EV = 1,00,000 30,000-5000
+= Rs. 1,25,000</t>
+  </si>
+  <si>
+    <t>The book value of a company's assets is Rs 8000 crores, and its total liabilities amount to Rs 3000 crores. If the company's market capitalization is Rs 11,000 crores, what is its Price-to-Book Value (P/B) ratio?</t>
+  </si>
+  <si>
+    <t>To calculate the Price-to-Book Value (P/B) Ratio, we use the formula:
+P/B Ratio = Market Capitalisation / Book Value of Equity
+Step 1: Calculate Book Value of Equity
+Book Value of Equity = Assets - Liabilities = 8000 3000 = Rs. 5000 crores
+Step 2: Calculate P/B Ratio
+P/B Ratio = Market Capitalisation / Book Value of Equity
+= 11000 cr / 5000 cr = 2.2x</t>
+  </si>
+  <si>
+    <t>A company has a Return on Equity (ROE) of 16%, Return on Capital Employed (ROCE) of 20%, Net Profit of Rs. 160,000, and EBIT of Rs. 250,000. If the company pays 10% annual interest on its debt, what is the total interest paid during the year?</t>
+  </si>
+  <si>
+    <t>Step 1: Use Return On Equity (ROE) to find Equity
+ROE = Net Profit? / Equity
+So Equity = Net Profit / ROE = 1,60,000/.16 = Rs 10,00,000
+Step 2: Use Return On Capital Employed (ROCE) to find Capital Employed
+ROCE = EBIT / Capital Employed
+So Capital Employed = EBIT / ROCE 2,50,000 / 0.2 = Rs 12,50,000
+Step 3: Use Capital Employed and Equity to find Debt
+Capital Employed = Equity + Debt
+Therefore Debt = Capital Employed - Equity = 12,50,000 10,00,000 = Rs 2,50,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A company has a net income of Rs. 360,000 and 6,00,000 outstanding shares.
+The Return on Equity (ROE) is 20%, and the book value per share is 25% of the market price. What is the market price per share? </t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>Step 1: Calculate Earnings Per Share (EPS)
+EPS = Net Income / No. of Shares
+= 360000/600000 Rs 0.60
+Step 2: Use Return on Equity (ROE) to find Book Value per Share
+ROE = EPS / Book value per share
+0.20=0.60 / Book value per share
+Book value per share = 0.60/0.20 = Rs. 3
+Step 3: Use the relationship between Book Value and Market Price
+Book Value = 25% of Market Price
+3 = 0.25 x Market Price
+Market price = 3/0.25 Rs 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the Earnings Yield of a company with market capitalization of Rs 15 lakhs and net profits of Rs 3 lakhs. </t>
+  </si>
+  <si>
+    <t>Earnings Yield = (Net Profit / Market Capitalization) * 100
+Given:
+• Market Capitalisation = Rs. 15,00,000
+• Net Profit = Rs. 3,00,000
+Earnings Yield (3,00,000/ 15,00,000)* 100
+= 0.2 x 100 = 20%</t>
+  </si>
+  <si>
+    <t>2.19x</t>
+  </si>
+  <si>
+    <t>1.44x</t>
+  </si>
+  <si>
+    <t>2.84x</t>
+  </si>
+  <si>
+    <t>1.02x</t>
+  </si>
+  <si>
+    <t>Rs. 63.74</t>
+  </si>
+  <si>
+    <t>Rs. 58</t>
+  </si>
+  <si>
+    <t>Rs. 47.22</t>
+  </si>
+  <si>
+    <t>Rs. 79.51</t>
+  </si>
+  <si>
+    <t>ROE is likely to be below 8%</t>
+  </si>
+  <si>
+    <t>ROE is likely to be above 10%</t>
+  </si>
+  <si>
+    <t>ROE will be 2%</t>
+  </si>
+  <si>
+    <t>ROE will be between 8 to 10%</t>
+  </si>
+  <si>
+    <t>Rs. 5,25,000</t>
+  </si>
+  <si>
+    <t>Rs. 7,85,600</t>
+  </si>
+  <si>
+    <t>Rs. 6, 15,000</t>
+  </si>
+  <si>
+    <t>Rs. 480000</t>
+  </si>
+  <si>
+    <t>Rs. 574000</t>
+  </si>
+  <si>
+    <t>Rs. 625000</t>
+  </si>
+  <si>
+    <t>Rs. 755000</t>
+  </si>
+  <si>
+    <t>Rs. 2,00,000</t>
+  </si>
+  <si>
+    <t>Rs, 5,00,000</t>
+  </si>
+  <si>
+    <t>Rs. 7,50,000</t>
+  </si>
+  <si>
+    <t>Rs. 4,75,000</t>
+  </si>
+  <si>
+    <t>Rs. 1,00,000</t>
+  </si>
+  <si>
+    <t>Rs. 1,35,000</t>
+  </si>
+  <si>
+    <t>Rs. 1,25,000</t>
+  </si>
+  <si>
+    <t>Rs. 65,000</t>
+  </si>
+  <si>
+    <t>2.2x</t>
+  </si>
+  <si>
+    <t>3.4x</t>
+  </si>
+  <si>
+    <t>1.6x</t>
+  </si>
+  <si>
+    <t>3x</t>
+  </si>
+  <si>
+    <t>Rs. 18500</t>
+  </si>
+  <si>
+    <t>Rs. 25000</t>
+  </si>
+  <si>
+    <t>Rs. 31000</t>
+  </si>
+  <si>
+    <t>Rs. 36500</t>
+  </si>
+  <si>
+    <t>Rs. 20</t>
+  </si>
+  <si>
+    <t>Rs. 9</t>
+  </si>
+  <si>
+    <t>Rs. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Total Assets of a company are Rs 100000 and the Total Liabilities are Rs 74000. Calculate the Equity to Asset Ratio. </t>
+  </si>
+  <si>
+    <t>Equity = Assets - Liabilities
+= 100000 - 74000
+= 26000
+Equity to Asset Ratio = Equity / Assets
+=26000/100000
+= 0.26</t>
+  </si>
+  <si>
+    <t>M/s. CORE INDUSTRIES has a debt of Rs. 3500 crores. The interest payable on this is at 8% p.a. Calculate the Interest Coverage Ratio if the expected EBIT is Rs. 320 crores.</t>
+  </si>
+  <si>
+    <t>Interest Coverage Ratio = EBIT / Interest Expense
+Interest expenses are 8% of 3500 cr = 280 cr
+Interest Coverage Ratio = 320 cr / 280 cr = 1.14</t>
+  </si>
+  <si>
+    <t>A company has declared 20% dividend. The face value of the share is Rs 5 and the dividend payout ratio is 50%. The current market price of the share is Rs. 100. Calculate the Earning Yield.</t>
+  </si>
+  <si>
+    <t>The company has declared 20% dividend on Rs. 5 face value. So the dividend is Re. 1 (20% of 5)
+Dividend Payout ratio = Dividend Per Share / EPS
+50% = 1/ EPS
+EPS=1/0.5
+EPS (Earning Per Share) = 2
+Earning Yield % = EPS / Stock Price x 100
+=2/100 x 100
+= .02 x 100 = 2%</t>
+  </si>
+  <si>
+    <t>The net profit of a company for the year was Rs 300 crores. It had 4,72,60,223 outstanding equity shares. The current price of the equity share is Rs 718. Find the P/E ratio of the share.</t>
+  </si>
+  <si>
+    <t>The formula for calculating PE Ratio is Market Price of the share / Earning Per Share (EPS)
+We know the market price. Lets calculate the EPS
+EPS = Profit / Number of shares = 300,00,00,000/ 4,72,60,223 = 63.478
+PE = 718/63.478 = 11.311</t>
+  </si>
+  <si>
+    <t>The face value of a share is Rs. 5 and the last dividend on it was 20%. Its dividend payout ratio was 60% and the current price is Rs. 90. Calculate the earning yield?</t>
+  </si>
+  <si>
+    <t>The company has declared 20% dividend on Rs. 5 face value. So the dividend is Re. 1 (20% of 5)
+Dividend Payout ratio = Dividend Per Share / EPS
+60%=1/EPS
+EPS=1/0.6
+EPS (Earning Per Share) = 1.66
+Earning Yield % = EPS / Stock Price x 100
+= 1.66 / 90 x 100
+= .0184x 1 00 = 1.84 %</t>
+  </si>
+  <si>
+    <t>The market price of a share is Rs. 42 and the PE ratio is 14. The dividend payout ratio is 50%. Calculate the dividend per share for this company.</t>
+  </si>
+  <si>
+    <t>Price Earning (PE) Ratio = Market Price / Earning Per Share (EPS)
+1442/ EPS
+So EPS = 42/14 = 3
+Dividend Payout Ratio = Dividend Per Share / EPS
+50% Dividend Per Share / 3
+So Dividend Per Share = 3 X 50% = Rs. 1.5</t>
+  </si>
+  <si>
+    <t>A shoe making company reported sales revenues of Rs 1,00,000 inclusive of indirect taxes of Rs. 15000 and direct taxes of Rs. 10000. Calculate the net sales?</t>
+  </si>
+  <si>
+    <t>All indirect taxes have to be deducted from the Gross Sales to get the Net Sales figure as these taxes are collected by the business for the government and don't belong to the business. Eg. GST
+Net Sales = Sales Indirect Taxes
+= 1,00,000 - 15,000
+= Rs. 85,000
+(Direct taxes are Income tax, MAT etc. which do not form a part of the sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A company has a share capital consisting of 80,000 shares. The Earnings Per Share (EPS) is Rs. 6, and the Price-to-Earnings (P/E) ratio is 12. Assuming the company has zero debt and no cash or cash equivalents, what is the Enterprise Value (EV) of the company? </t>
+  </si>
+  <si>
+    <t>Step 1: Calculate Market Price per Share using the PE Ratio formula
+P/E Ratio = Market Price per Share / EPS
+Therefore : Market Price per Share = EPS * P/E Ratio = 6 x 12 = Rs. 72
+Step 2: Calculate Market Capitalisation
+Market Ca p= Market Price per Share
+Step 3: Calculate Enterprise Value (EV)
+Number of Shares = 72 x 80,000 = Rs. 5,760,000
+EV = Market Cap + Total Debt - Cash and Cash Equivalents
+Since both debt and cash are zero:
+EV = 5760,000+ 0 0 = Rs. 57,60,000</t>
+  </si>
+  <si>
+    <t>Calculate the Net Profit margin for the following: A company's sales are 250% of operating profit, while its net profit amounts to one-fourth of operating profit.</t>
+  </si>
+  <si>
+    <t>Let Operating Profit = Rs. 100 (For easy calculations)
+Then:
+• Sales = 2.5 x 100 = Rs. 250
+• Net Profit = (1/4) x 100 = Rs. 25
+Net Profit Margin = (Net Profit / Sales?) * 100
+= (25/250) x 100 = 10%</t>
+  </si>
+  <si>
+    <t>Rs. 2.5</t>
+  </si>
+  <si>
+    <t>Rs. 1.5</t>
+  </si>
+  <si>
+    <t>Rs. 75,000</t>
+  </si>
+  <si>
+    <t>Rs. 85,000</t>
+  </si>
+  <si>
+    <t>Rs. 34,75,000</t>
+  </si>
+  <si>
+    <t>Rs. 68,22,000</t>
+  </si>
+  <si>
+    <t>Rs. 45,00,000</t>
+  </si>
+  <si>
+    <t>Rs. 57,60,000</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1018,6 +1416,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1033,10 +1434,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2282,7 +2679,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2578,29 +2975,693 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E2F324-04E0-4717-A76A-F3E28E20A349}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5703125" customWidth="1"/>
+    <col min="3" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="77.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="4">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.105</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.124</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE1BC95-7380-4A63-9900-50895A7752AE}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5703125" customWidth="1"/>
+    <col min="3" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="77.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3.41</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.23</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1.77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="4">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.31</v>
+      </c>
+      <c r="D5" s="4">
+        <v>11.31</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.131</v>
+      </c>
+      <c r="F5" s="4">
+        <v>113.1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.84E-2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.09E-2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C11" s="6">
         <v>0.5</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D11" s="6">
         <v>0.2</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E11" s="6">
         <v>0.25</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F11" s="6">
         <v>0.75</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>177</v>
       </c>
     </row>

--- a/Data/Numericals.xlsx
+++ b/Data/Numericals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acldigital1-my.sharepoint.com/personal/sathishkumarr_acldigital1_onmicrosoft_com/Documents/Study/_NISM Certifications/_PGPFP/Course/Term 2/Research Analyst/Numericals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{85BC9775-B3CC-4C47-9973-3760C76C5C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E685E9A-2920-4ED3-A7FF-55883D17C07D}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{85BC9775-B3CC-4C47-9973-3760C76C5C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE70224-8A09-4DE1-B3BB-8EAE7688A3ED}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{B3B2EAEB-3D4F-44E9-A7BC-7C78BD8AFC15}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="5" xr2:uid="{B3B2EAEB-3D4F-44E9-A7BC-7C78BD8AFC15}"/>
   </bookViews>
   <sheets>
     <sheet name="Numericals 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Numericals 4" sheetId="4" r:id="rId4"/>
     <sheet name="Numericals 5" sheetId="5" r:id="rId5"/>
     <sheet name="Numericals 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Numericals 7" sheetId="7" r:id="rId7"/>
+    <sheet name="Numericals 8" sheetId="8" r:id="rId8"/>
+    <sheet name="Numericals 9" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="411">
   <si>
     <t>Questiod_ID</t>
   </si>
@@ -1342,6 +1345,486 @@
   </si>
   <si>
     <t>Rs. 57,60,000</t>
+  </si>
+  <si>
+    <t>Find the market price of a company's share from the following data: Total Assets: Rs. 50,00,000 Earning Per Share (EPS) : Rs. 2 Net Income: Rs. 4,00,000 Return on equity 20% Price to Book Value: 5</t>
+  </si>
+  <si>
+    <t>To find the above answer, we need to find the Book Value per Share.
+Let's find the number of shares first
+Earnings Per share = Net Income/No of Shares outstanding
+2 = 4,00,000/No of shares outstanding
+No of Shares Outstanding = 400000/2 = 2,00,000
+Now let's find the book value per share, before which we'll have to find book value of total equity
+Return on Equity = Net Income/Book Value of Equity
+20% = 400000/Book Value of Equity
+Book Value of Equity = 400000/.20 = 20,00,000
+Now, Book value per share = Book Value of Equity/No of Shares Outstanding
+Book Value per share=2000000/200000 = 10
+Now let's finally find the market price per share
+Market price per share = Book Value per share x Price to Book Value
+Market Price per share = 10 x 5 = 50</t>
+  </si>
+  <si>
+    <t>The EV/EBIT ratio in an industry is 10.0X. A company from the in industry reported an EBIT of Rs 500 crores. The company has net debt of Rs 800 crores. What is the value of the company's equity?</t>
+  </si>
+  <si>
+    <t>Enterprise Value (EV) Value of Equity + Value of Debt
+The EV/EBIT = 10
+So the EV is EBIT X 10 = 500 crores X 10 = Rs 5000 crores
+EV = Value of Equity + Value of Debt
+So Value of Equity = EV - Value of Debt
+= 5000 cr - 800 cr Rs 4200 crores</t>
+  </si>
+  <si>
+    <t>The share price of a company is Rs. 35 and currently it has 10 million shares trading. The company has assets worth Rs. 120 million and liabilities worth Rs. 40 million. Calculate the Price to Book Ratio.</t>
+  </si>
+  <si>
+    <t>Market Cap = No. of shares x Market price of shares = 10 million x 35 = 350 million
+Net worth = Assets - Liabilites = 120 million - 40 million = 80 million
+Price to book value ratio = Market capitalization/ Net worth
+= 350 million / 80 million
+= 4.37x</t>
+  </si>
+  <si>
+    <t>Rs. 50</t>
+  </si>
+  <si>
+    <t>Rs. 35</t>
+  </si>
+  <si>
+    <t>Rs. 75</t>
+  </si>
+  <si>
+    <t>Rs. 1300 crores</t>
+  </si>
+  <si>
+    <t>Rs. 5800 crores</t>
+  </si>
+  <si>
+    <t>Rs. 4200 crores</t>
+  </si>
+  <si>
+    <t>Rs. 2700 crores</t>
+  </si>
+  <si>
+    <t>5.63x</t>
+  </si>
+  <si>
+    <t>4.37x</t>
+  </si>
+  <si>
+    <t>5.99x</t>
+  </si>
+  <si>
+    <t>3.84x</t>
+  </si>
+  <si>
+    <t>A textile marketing company reports total sales revenue of Rs. 2,00,000, which includes indirect taxes of Rs. 20,000 and direct taxes of Rs.15,000. What is the company's net sales?</t>
+  </si>
+  <si>
+    <t>A company has Book Value per share of Rs. 18. Its Market capitalization is of Rs. 50 lakhs and Networth of Rs.10 lakhs. Calculate the Price to book value ratio of this company.</t>
+  </si>
+  <si>
+    <t>The Market Capitalisation of a company is Rs 8,00,000. Its Price to Book value ratio is 10 and the Book Value is Rs. 14. Calculate the Net Worth of the company.</t>
+  </si>
+  <si>
+    <t>The Networth of a business is Rs. 2,00,000 and the debt on Balance Sheet is Rs 2,00,000. The Market Capitalisation is Rs. 8,00,000. Calculate the Capital Employed by the business.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The umbrella market in India is dominated by three major players who have a combined revenue of Rs. 1500 crores. It is estimated that other players contribute to 40% of the market share. Calculate the total market size of the umbrella market in India? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miss. Z invest Rs. 30,000 at the rate of 8% per annum. What would be the future value of such investment after 5 years? </t>
+  </si>
+  <si>
+    <t>Calculate the Net Profit margin in the business with the given data - The Sales are 200% of Operating Profits and the Operating Profit is 400% of Net Profit.</t>
+  </si>
+  <si>
+    <t>A company operates three business divisions valued at Rs. 1,500 crores, Rs. 2,800 crores, and Rs. 2,200 crores respectively. Its corporate division incurs a net expense of Rs. 300 crores. If the EV/EBIT ratio is 6x, what is the fair enterprise value of the company?</t>
+  </si>
+  <si>
+    <t>With a market capitalization of Rs. 225 crores and a price-to-earnings (P/E) ratio of 15x, a company has 5 crore shares outstanding. Which of the following is closest to its earnings per share (EPS)?</t>
+  </si>
+  <si>
+    <t>A company's asset to equity ratio is 2.0, and its total assets amount to Rs 40,00,000. The net income of the company is Rs 600,000, and the earnings per share (EPS) is reported as Rs 1.00. What is the Return on Equity (ROE) for the company?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha Ventures Ltd reported standalone revenue of Rs. 5100 crores. It owns 80% of Beta Corp and 25% of Gamma Associates (a joint venture). Beta and Gamma reported revenues of Rs. 2,500 crores and Rs. 1,300 crores respectively. Calculate Alpha Ventures consolidated revenue. </t>
+  </si>
+  <si>
+    <t>A company has the following details: paid-up capital Rs.25,00,000 (Face value Rs. 5 per share), EPS Rs. 10, P/E 15, zero debt, and cash of Rs. 50 lakhs. Determine the Enterprise Value (EV).</t>
+  </si>
+  <si>
+    <t>Determine the weighted average cost of capital of a company given that its cost of equity is 17%, its cost of debt is 11%, and the proportion of debt in total capital is 60% (assume no taxes).</t>
+  </si>
+  <si>
+    <t>We can calculate Weighted Average Cost of Capital (WACC) using the formula:
+WACC = (E/V x Ke) + (D/V * Kd * (1 - Tax rate))
+Since tax rate is not given, we will ignore it for this calculation.
+Given:
+• Cost of equity (Ke) = 17% = 0.17
+Cost of debt (Kd) = 11% = 0.11
+• Weight of debt (D/V) = 60% = 0.6
+• Weight of equity (E/V) 10.6 0.4
+Now plug into the formula:
+WACC = (0.4 x 0.17) + (0.6 x 0.11)
+= 0.068 +0.066
+= 0.134 or 13.4%</t>
+  </si>
+  <si>
+    <t>Enterprise Value (EV) = Market cap - Cash + Debt
+First, calculate the market capitalization:
+Number of shares = Paid-up capital / Face value = 25,00,000/ 5 = 5,00,000 shares
+Market price per share= EPS * P/E ratio = 10 x 15 150
+Market capitalization = No. of shares x Market price per share = 5,00,000 x 150 7,50,00,000 (Rs 7.5 crore)
+Enterprise Value (EV) = Market cap - Cash + Debt = 7,50,00,000 50,000,00 + 0 = Rs 7 crores.</t>
+  </si>
+  <si>
+    <t>To calculate the consolidated revenue of Alpha Ventures Ltd, we need to follow consolidation rules based on the percentage of ownership:
+1. If ownership is &gt;50% → Full consolidation (100% of the subsidiary's revenue is added)
+2. If ownership is 20%-50% → Equity method → No revenue consolidation, only share of profit is shown separately (so, revenue of associate is not added) Therefore, in the above case, only Beta Corp revenue will be added and not of Gamma Associates.
+Consolidated Revenue = Alpha Ventures Revenue + Beta Corp Revenue = Rs. 5100 + Rs 2500 = Rs 7600 crores</t>
+  </si>
+  <si>
+    <t>To calculate Return on Equity (ROE) we use the formula:
+ROE = (Net Income / Shareholders' Equity) * 100
+Step 1: Find Shareholders Equity
+Asset to Equity Ratio = Total Assets/ Equity ?: This is given as 2
+Equity = Total Assets / 2
+=40,00,000/ 2 = Rs 20,00,000
+Step 2: Calculate ROE
+ROE= (Net Income / Share holder's Equity ) x 100
+= (6,00,000/ 20,00,000) x 100 = 30%</t>
+  </si>
+  <si>
+    <t>Let's first calculate Market Price per Share.
+Market Price per Share = Market Capitalisation? / Number of Shares
+= 225 crores / 5 crores = Rs 45
+We will now use P/E ratio to calculate EPS
+P/E Ratio = Market Price per share / EPS
+Therefore EPS = Market price per share / PE ratio
+= 45/15
+= Rs 3</t>
+  </si>
+  <si>
+    <t>First calculate the Total Operating Value:
+Rs 1500 + Rs 2800 + Rs 2200 = Rs 6500 crores
+The Corporate division has a net EBIT expense = Rs 300 crores
+Given that EV/EBIT = 6x
+Capitalised corporate cost = 300 x 6 = Rs 1800 crores
+Final Enterprise Value Calculation: The fair enterprise value is the sum of the productive parts minus the capitalized cost of the corporate overhead. EV 6500-1800 Rs 4700 crores</t>
+  </si>
+  <si>
+    <t>Lets assume that the Operating Profit is Rs. 100
+Sales are 200% of Operating Profit. So Sales will be Rs. 200 (100 x 200%)
+Operating Profit is 400% of Net Profit. So Net Profit is 1/4 of Rs. 100 = Rs. 25
+On a Sale of Rs. 200, the Net Profit is Rs. 25
+So the Net Profit margin is 12.5% (25/200 x 100)</t>
+  </si>
+  <si>
+    <t>The formula for calculating Future Value is : FV = PV (1+r)"
+PV = Present Value; r = yearly interest rate (8% = .08); n = number of years = 5
+Substituting:
+FV = 30,000 (1 + .08) ^ 5
+FV = 30000 (1.08) ^ 5
+On the Scientific Calculator of your computer press: 1.08, X^Y, 5 = 1.4693
+FV 30000 x 1.4693 Rs. 44,079</t>
+  </si>
+  <si>
+    <t>The other players contribute 40% of the market share. This means the three major players have the balance 60% of the umbrella market. This 60% is equal to Rs. 1500
+crores.
+Therefore, if 60% = 1500 crores, 100% (Total Market size) will be equal to how much?
+1500/60 x 100 = Rs. 2500 crores.</t>
+  </si>
+  <si>
+    <t>Capital Employed can be calculated using two formulas.
+1) Capital Employed = Total Assets - Current Liabilities
+2) Capital Employed Total Equity + Total Debt
+Here we use the second formula.
+Capital Employed = Total Equity + Total Debt
+=200000 + 200000 = 400000</t>
+  </si>
+  <si>
+    <t>Price to book value ratio = Market capitalization/ Net-worth
+10 = 8,00,000/Net-worth
+Net-worth = 800000/10 80000</t>
+  </si>
+  <si>
+    <t>Price to book value ratio can be calculated using: Market capitalization / Networth
+50,000,00 / 10,00,000 = 5</t>
+  </si>
+  <si>
+    <t>Net sales are calculated by removing indirect taxes (like GST, excise duty) from total sales revenue, because they don't belong to the company and are collected on behalf of the Government and needs to be paid back to the Government.
+Here, sales revenue = Rs 2,00,000 (includes indirect taxes of Rs 20,000). So, Net Sales = 2,00,000-20,000 = Rs 1,80,000.
+Direct taxes are on profits, not deducted from sales, so they don't affect net sales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rs. 1,65,000 </t>
+  </si>
+  <si>
+    <t>Rs. 1,80,000</t>
+  </si>
+  <si>
+    <t>Rs. 2,35,000</t>
+  </si>
+  <si>
+    <t>Rs. 40,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rs. 50,000 </t>
+  </si>
+  <si>
+    <t>Rs. 60,000</t>
+  </si>
+  <si>
+    <t>Rs. 80,000</t>
+  </si>
+  <si>
+    <t>Rs. 6,00,000</t>
+  </si>
+  <si>
+    <t>Rs. 4,00,000</t>
+  </si>
+  <si>
+    <t>Rs. 1020 crores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rs. 3500 crores </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rs. 2100 crores </t>
+  </si>
+  <si>
+    <t>Rs. 2500 crores</t>
+  </si>
+  <si>
+    <t>Rs. 37,816</t>
+  </si>
+  <si>
+    <t>Rs. 42,560</t>
+  </si>
+  <si>
+    <t>Rs. 53,100</t>
+  </si>
+  <si>
+    <t>Rs. 44,079</t>
+  </si>
+  <si>
+    <t>Rs. 7,500 crores</t>
+  </si>
+  <si>
+    <t>Rs. 12,200 crores</t>
+  </si>
+  <si>
+    <t>Rs. 28,800 crores</t>
+  </si>
+  <si>
+    <t>Rs. 4,700 crores</t>
+  </si>
+  <si>
+    <t>Rs. 1.20</t>
+  </si>
+  <si>
+    <t>Rs 3</t>
+  </si>
+  <si>
+    <t>Rs. 5100 crores</t>
+  </si>
+  <si>
+    <t>Rs. 7600 crores</t>
+  </si>
+  <si>
+    <t>Rs. 8900 crores</t>
+  </si>
+  <si>
+    <t>Rs. 6300 crores</t>
+  </si>
+  <si>
+    <t>Rs. 5.75 crore</t>
+  </si>
+  <si>
+    <t>Rs. 7 crore</t>
+  </si>
+  <si>
+    <t>Rs. 6.66 crore</t>
+  </si>
+  <si>
+    <t>Rs. 8 crore</t>
+  </si>
+  <si>
+    <t>An investor bought 100 shares of a company of face value of Rs. 2 at Rs 10,000. Calculate the dividend yield on the value invested in these shares if the company declares 300% dividend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total liabilities in a business are Rs. 12000 and the total assets are Rs. 16000. What is the Asset to Equity ratio? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A company has a market cap of Rs. 5,000,000, with an EPS of Rs. 12, Dividend per share of Rs. 4, and a book value per share of Rs. 30. Based on this information, what is the Price-to-Book (P/B) ratio? </t>
+  </si>
+  <si>
+    <t>Given that a stock has an EPS of Rs. 12 and a market price of Rs. 360, what is its earnings yield?</t>
+  </si>
+  <si>
+    <t>A company has a paid-up capital of Rs.25,00,000 with a face value of Rs.10 per share. If its earnings per share (EPS) are Rs. 7 and the book value per share is Rs. 25, what is the return on equity (ROE) of the company?</t>
+  </si>
+  <si>
+    <t>If an investment of Rs. 80 in a mutual fund grows to Rs. 105 over a period of 4 years, what is the compounded annual growth rate (CAGR) of the investment?</t>
+  </si>
+  <si>
+    <t>The EBITDA of a company is Rs. 275 crores and the EV/EBITDA ratio is 6x. The company has a net debt of Rs 520 crores. Calculate the value of its equity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current liabilities of a business are Rs. 33000, the inventory is Rs. 13000 and the Current Ratio is 3. Calculate the Quick Ratio. </t>
+  </si>
+  <si>
+    <t>The EBIT % of a business is 50% with EBIT levels of Rs 200000. The Net Profit margin of this company is 20%. No. of shares outstanding are 20000. The Retention Ratio is 60%. Calculate the Dividend Per Share.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahul invests Rs. 75000 at the rate of 6% p.a. Calculate the future value of his investments after 10 years. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find out the Cost of Equity if the risk free rate is 5%, the Market risk premium is 8% and the Beta is 0.60. </t>
+  </si>
+  <si>
+    <t>The Cost of Equity can be calculated using the Capital Asset Pricing Model (CAPM) formula:
+Cost of Equity (Re) = rf + ẞ (rm -rf)
+Where:
+• rf = Risk Free Rate = 5%
+• rm -rf = Market Risk Premium = 8%
+• ẞ= Beta = 0.60
+Substituting the values:
+re = 5%+(0.60×8%)
+re= 5%+4.8%
+re 9.8%</t>
+  </si>
+  <si>
+    <t>The EBIT is Rs 200000 and this is 50% of the business ie. 50% of sales.
+So Sales = Rs 400000 (200000 / 50 x 100)
+Net Profit margin is 20% ie 20% of Sales Rs 400000
+20% of Rs 400000 = 80000
+EPS = Net Profit / No. of Shares
+=80000/20000 = 4
+Retention Ratio is 60% which means the Dividend Payout Ration is 40% (100-60)
+40% dividend is paid from the earnings.
+40% of EPS ie. 40% of 4 = Rs 1.60 is the Dividend Paid per share</t>
+  </si>
+  <si>
+    <t>Current Ratio = Current Assets / Current Liabilities
+3 = Current Assets / 33000
+Current Assets = 33000 x 3 = 99,000
+Quick Ratio = (Current Assets - Inventories) / Current Liabilities
+= (99000-13000) / 33000
+= 86000/33000
+= 2.60</t>
+  </si>
+  <si>
+    <t>It is given that EV/EBITDA = 6
+EBITDA is given as Rs. 275 crores
+Therefore EV / 275 crores = 6
+EV (Enterprise Value) = 275 x 6 = 1650 crores
+Enterprise Value = Value of Equity + Value of Debt
+1650 crores = Value of Equity + 520 crores
+Value of Equity = 1650 - 520 = Rs. 1130 crores</t>
+  </si>
+  <si>
+    <t>The compounded annual growth rate (CAGR) is calculated using the formula:
+CAGR= (Final Value / Initial Value) ^ 1/n -1
+(n is the period in years)
+CAGR = (105/80) ^1/4 -1
+= (1.3125)^0.25 -1
+(On the scientific calculator of your system: Press 1.3125, x^y, 0.25 and you will get 1.0703)
+= 1.0703 -1
+= 0.0703 or 7.03%</t>
+  </si>
+  <si>
+    <t>Paid-up capital = Rs 25,00,000 with face value Rs 10 → Number of shares = 2,50,000.
+Book value per share = Rs 25 → Total equity = 2,50,000 × 25 = Rs 62,50,000.
+EPS = Rs 7 → Net profit = 2,50,000 x 7 = Rs 17,50,000.
+Return on Equity (ROE) = Net Profit ÷ Equity = 17,50,000 62,50,000 0.28 or 28%.
+OR
+Return on Equity (ROE) is calculated as Earnings Per Share divided by Book Value per Share. Here, EPS is Rs 7 and Book Value per Share is Rs 25.
+ROE = 7 ÷ 25 = 0.28 or 28%.</t>
+  </si>
+  <si>
+    <t>We assume Market Price = Book Value = Rs 360
+Earnings Yield = (EPS / Market Price) x 100
+= (12/360) x 100 = 3.33%</t>
+  </si>
+  <si>
+    <t>To calculate the Price to Book Value (P/B) ratio, use the following formula:
+P/B Ratio = Market Price per Share / Book Value per Share
+We do not have the Market Price per Share
+Market Price per Share can be calculated as Market Capitalisation / Number of Shares
+But, number of shares is also not provided.
+Therefore, the data is insufficient to for calculations.</t>
+  </si>
+  <si>
+    <t>Asset-to-Equity Ratio = Total Assets / Shareholders Equity
+Shareholders Equity = Total Assets - Total Liabilities
+= 16000-12000 = Rs. 4000
+Asset-to-Equity Ratio = Total Assets / Shareholders Equity
+= 16000 / 4000 = 4</t>
+  </si>
+  <si>
+    <t>Dividend Yield = Dividend Received / Amount Invested x 100
+300% dividend on Rs. 2 face value is Rs. 6 (2 x 300%).
+Amount of dividend = Rs. 6 x 100 (No. of shares) = Rs. 600
+Amount invested = Rs. 10,000
+Dividend Yield = 600 / 10000 x 100 = 6%</t>
+  </si>
+  <si>
+    <t>Rs. 0.50</t>
+  </si>
+  <si>
+    <t>Rs. 25</t>
+  </si>
+  <si>
+    <t>Cannot be calculated as data provided is insufficient</t>
+  </si>
+  <si>
+    <t>Cannot be calculated with the given data</t>
+  </si>
+  <si>
+    <t>Rs. 895 crores</t>
+  </si>
+  <si>
+    <t>Rs. 1275 crores</t>
+  </si>
+  <si>
+    <t>Rs. 960 crores</t>
+  </si>
+  <si>
+    <t>Rs. 1130 crores</t>
+  </si>
+  <si>
+    <t>Rs. 3.50</t>
+  </si>
+  <si>
+    <t>Rs 0.50</t>
+  </si>
+  <si>
+    <t>Rs 2</t>
+  </si>
+  <si>
+    <t>Rs. 98,540</t>
+  </si>
+  <si>
+    <t>Rs. 1,34,313</t>
+  </si>
+  <si>
+    <t>Rs. 1,12,500</t>
+  </si>
+  <si>
+    <t>Rs. 1,48,650</t>
+  </si>
+  <si>
+    <t>The formula for calculating Future Value is FV=PV(1+r)"
+PV = Present Value; r = yearly interest rate (6% = .06); n = number of years
+Substituting :
+FV = 75000 (1 + .06) ^ 10
+FV = 75000 (1.06) ^ 10
+On the Scientific Calculator of your computer press 1.06, X^Y, 10 = 1.790847
+FV = 75000 x 1.79 = 1,34,313</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1419,6 +1902,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1434,6 +1920,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3668,4 +4158,922 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFFB895-0D8C-40CE-B8A7-936F44231A9E}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5703125" customWidth="1"/>
+    <col min="3" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="77.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="300" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.1207</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.1108</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.105</v>
+      </c>
+      <c r="E11" s="4">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>8.6499999999999994E-2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536E02DC-EEA3-4625-9F8B-886500B5C873}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5703125" customWidth="1"/>
+    <col min="3" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="77.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2.78</v>
+      </c>
+      <c r="D3" s="10">
+        <v>10</v>
+      </c>
+      <c r="E3" s="10">
+        <v>5</v>
+      </c>
+      <c r="F3" s="10">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="F11" s="6">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DFACB5-C04B-4130-BDA4-6B3436612B8F}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="82.42578125" customWidth="1"/>
+    <col min="3" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="77.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2.44</v>
+      </c>
+      <c r="D3" s="10">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1.33</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6.4699999999999994E-2</v>
+      </c>
+      <c r="D7" s="4">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>